--- a/exercise/Admin/Admin Penjualan/Tes Excel Admin Penjualan 8.xlsx
+++ b/exercise/Admin/Admin Penjualan/Tes Excel Admin Penjualan 8.xlsx
@@ -1,21 +1,20 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="26731"/>
-  <workbookPr codeName="ThisWorkbook" defaultThemeVersion="166925"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
+  <fileVersion appName="xl" lastEdited="6" lowestEdited="6" rupBuild="14420"/>
+  <workbookPr codeName="ThisWorkbook"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\admin\Downloads\Tes Excel Admin Penjualan 8\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Pemrograman\Excel\excel\exercise\Admin\Admin Penjualan\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0FAE3F38-675E-4B11-8E44-88BF1B96B38D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160"/>
   </bookViews>
   <sheets>
     <sheet name="Soal" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="191029"/>
+  <calcPr calcId="152511"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -377,7 +376,7 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <numFmts count="3">
     <numFmt numFmtId="41" formatCode="_-* #,##0_-;\-* #,##0_-;_-* &quot;-&quot;_-;_-@_-"/>
     <numFmt numFmtId="164" formatCode="_(* #,##0.00_);_(* \(#,##0.00\);_(* &quot;-&quot;??_);_(@_)"/>
@@ -548,7 +547,7 @@
     <xf numFmtId="41" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="31">
+  <cellXfs count="30">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
@@ -597,9 +596,6 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" indent="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="1" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
@@ -612,23 +608,23 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="5" xfId="4" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="3" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="5" xfId="4" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="5">
@@ -636,7 +632,7 @@
     <cellStyle name="Comma [0]" xfId="3" builtinId="6"/>
     <cellStyle name="Hyperlink" xfId="4" builtinId="8"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
-    <cellStyle name="Normal 2 2" xfId="2" xr:uid="{00000000-0005-0000-0000-000002000000}"/>
+    <cellStyle name="Normal 2 2" xfId="2"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -947,7 +943,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet1">
     <tabColor theme="0"/>
   </sheetPr>
@@ -970,10 +966,10 @@
       <c r="D1" s="10" t="s">
         <v>56</v>
       </c>
-      <c r="E1" s="30" t="s">
+      <c r="E1" s="26" t="s">
         <v>57</v>
       </c>
-      <c r="F1" s="25"/>
+      <c r="F1" s="27"/>
       <c r="G1" s="2"/>
       <c r="H1" s="2"/>
       <c r="I1" s="2"/>
@@ -988,34 +984,34 @@
     </row>
     <row r="2" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A2" s="3"/>
-      <c r="B2" s="26" t="s">
+      <c r="B2" s="25" t="s">
         <v>0</v>
       </c>
-      <c r="C2" s="26" t="s">
+      <c r="C2" s="25" t="s">
         <v>1</v>
       </c>
-      <c r="D2" s="26" t="s">
+      <c r="D2" s="25" t="s">
         <v>2</v>
       </c>
-      <c r="E2" s="26" t="s">
+      <c r="E2" s="25" t="s">
         <v>3</v>
       </c>
-      <c r="F2" s="26" t="s">
+      <c r="F2" s="25" t="s">
         <v>4</v>
       </c>
-      <c r="G2" s="27" t="s">
+      <c r="G2" s="28" t="s">
         <v>5</v>
       </c>
-      <c r="H2" s="26" t="s">
+      <c r="H2" s="25" t="s">
         <v>6</v>
       </c>
-      <c r="I2" s="26" t="s">
+      <c r="I2" s="25" t="s">
         <v>7</v>
       </c>
-      <c r="J2" s="26" t="s">
+      <c r="J2" s="25" t="s">
         <v>8</v>
       </c>
-      <c r="K2" s="26" t="s">
+      <c r="K2" s="25" t="s">
         <v>9</v>
       </c>
       <c r="L2" s="3"/>
@@ -1027,16 +1023,16 @@
     </row>
     <row r="3" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A3" s="4"/>
-      <c r="B3" s="26"/>
-      <c r="C3" s="26"/>
-      <c r="D3" s="26"/>
-      <c r="E3" s="26"/>
-      <c r="F3" s="26"/>
-      <c r="G3" s="28"/>
-      <c r="H3" s="26"/>
-      <c r="I3" s="26"/>
-      <c r="J3" s="26"/>
-      <c r="K3" s="26"/>
+      <c r="B3" s="25"/>
+      <c r="C3" s="25"/>
+      <c r="D3" s="25"/>
+      <c r="E3" s="25"/>
+      <c r="F3" s="25"/>
+      <c r="G3" s="29"/>
+      <c r="H3" s="25"/>
+      <c r="I3" s="25"/>
+      <c r="J3" s="25"/>
+      <c r="K3" s="25"/>
       <c r="L3" s="4"/>
       <c r="M3" s="4"/>
       <c r="N3" s="4"/>
@@ -1055,15 +1051,33 @@
       <c r="D4" s="6" t="s">
         <v>10</v>
       </c>
-      <c r="E4" s="19"/>
-      <c r="F4" s="19"/>
-      <c r="G4" s="24"/>
+      <c r="E4" s="19" t="str">
+        <f>IF(LEFT(D4,1)="L","Ligna",IF(LEFT(D4,1)="O","Olympic",IF(LEFT(D4,1)="G","Garuda")))</f>
+        <v>Ligna</v>
+      </c>
+      <c r="F4" s="19" t="str">
+        <f>VLOOKUP(MID(D4,2,2),$C$17:$D$21,2,FALSE)</f>
+        <v>ALMARI</v>
+      </c>
+      <c r="G4" s="23">
+        <f>MID(D4,4,3)*1000</f>
+        <v>350000</v>
+      </c>
       <c r="H4" s="17">
         <v>6</v>
       </c>
-      <c r="I4" s="21"/>
-      <c r="J4" s="22"/>
-      <c r="K4" s="23"/>
+      <c r="I4" s="20">
+        <f>G4*H4</f>
+        <v>2100000</v>
+      </c>
+      <c r="J4" s="21">
+        <f>I4*(VLOOKUP(MID(D4,9,1),$C$23:$D$27,2,FALSE))</f>
+        <v>420000</v>
+      </c>
+      <c r="K4" s="22">
+        <f>I4-J4</f>
+        <v>1680000</v>
+      </c>
       <c r="L4" s="5"/>
       <c r="M4" s="5"/>
       <c r="N4" s="14"/>
@@ -1082,15 +1096,33 @@
       <c r="D5" s="6" t="s">
         <v>11</v>
       </c>
-      <c r="E5" s="19"/>
-      <c r="F5" s="19"/>
-      <c r="G5" s="20"/>
+      <c r="E5" s="19" t="str">
+        <f t="shared" ref="E5:E15" si="0">IF(LEFT(D5,1)="L","Ligna",IF(LEFT(D5,1)="O","Olympic",IF(LEFT(D5,1)="G","Garuda")))</f>
+        <v>Garuda</v>
+      </c>
+      <c r="F5" s="19" t="str">
+        <f t="shared" ref="F5:F15" si="1">VLOOKUP(MID(D5,2,2),$C$17:$D$21,2,FALSE)</f>
+        <v>RAK BUKU</v>
+      </c>
+      <c r="G5" s="23">
+        <f t="shared" ref="G5:G15" si="2">MID(D5,4,3)*1000</f>
+        <v>250000</v>
+      </c>
       <c r="H5" s="17">
         <v>7</v>
       </c>
-      <c r="I5" s="21"/>
-      <c r="J5" s="22"/>
-      <c r="K5" s="23"/>
+      <c r="I5" s="20">
+        <f t="shared" ref="I5:I15" si="3">G5*H5</f>
+        <v>1750000</v>
+      </c>
+      <c r="J5" s="21">
+        <f t="shared" ref="J5:J15" si="4">I5*(VLOOKUP(MID(D5,9,1),$C$23:$D$27,2,FALSE))</f>
+        <v>262500</v>
+      </c>
+      <c r="K5" s="22">
+        <f t="shared" ref="K5:K15" si="5">I5-J5</f>
+        <v>1487500</v>
+      </c>
       <c r="L5" s="5"/>
       <c r="M5" s="5"/>
       <c r="N5" s="5"/>
@@ -1109,15 +1141,33 @@
       <c r="D6" s="6" t="s">
         <v>12</v>
       </c>
-      <c r="E6" s="19"/>
-      <c r="F6" s="19"/>
-      <c r="G6" s="20"/>
+      <c r="E6" s="19" t="str">
+        <f t="shared" si="0"/>
+        <v>Olympic</v>
+      </c>
+      <c r="F6" s="19" t="str">
+        <f t="shared" si="1"/>
+        <v>MEJA BELAJAR</v>
+      </c>
+      <c r="G6" s="23">
+        <f t="shared" si="2"/>
+        <v>475000</v>
+      </c>
       <c r="H6" s="17">
         <v>10</v>
       </c>
-      <c r="I6" s="21"/>
-      <c r="J6" s="22"/>
-      <c r="K6" s="23"/>
+      <c r="I6" s="20">
+        <f t="shared" si="3"/>
+        <v>4750000</v>
+      </c>
+      <c r="J6" s="21">
+        <f t="shared" si="4"/>
+        <v>950000</v>
+      </c>
+      <c r="K6" s="22">
+        <f t="shared" si="5"/>
+        <v>3800000</v>
+      </c>
       <c r="L6" s="5"/>
       <c r="M6" s="5"/>
       <c r="N6" s="5"/>
@@ -1136,15 +1186,33 @@
       <c r="D7" s="6" t="s">
         <v>13</v>
       </c>
-      <c r="E7" s="19"/>
-      <c r="F7" s="19"/>
-      <c r="G7" s="20"/>
+      <c r="E7" s="19" t="str">
+        <f t="shared" si="0"/>
+        <v>Ligna</v>
+      </c>
+      <c r="F7" s="19" t="str">
+        <f t="shared" si="1"/>
+        <v>MEJA KERJA</v>
+      </c>
+      <c r="G7" s="23">
+        <f t="shared" si="2"/>
+        <v>760000</v>
+      </c>
       <c r="H7" s="17">
         <v>7</v>
       </c>
-      <c r="I7" s="21"/>
-      <c r="J7" s="22"/>
-      <c r="K7" s="23"/>
+      <c r="I7" s="20">
+        <f t="shared" si="3"/>
+        <v>5320000</v>
+      </c>
+      <c r="J7" s="21">
+        <f t="shared" si="4"/>
+        <v>532000</v>
+      </c>
+      <c r="K7" s="22">
+        <f t="shared" si="5"/>
+        <v>4788000</v>
+      </c>
       <c r="L7" s="5"/>
       <c r="M7" s="5"/>
       <c r="N7" s="5"/>
@@ -1163,15 +1231,33 @@
       <c r="D8" s="6" t="s">
         <v>11</v>
       </c>
-      <c r="E8" s="19"/>
-      <c r="F8" s="19"/>
-      <c r="G8" s="20"/>
+      <c r="E8" s="19" t="str">
+        <f t="shared" si="0"/>
+        <v>Garuda</v>
+      </c>
+      <c r="F8" s="19" t="str">
+        <f t="shared" si="1"/>
+        <v>RAK BUKU</v>
+      </c>
+      <c r="G8" s="23">
+        <f t="shared" si="2"/>
+        <v>250000</v>
+      </c>
       <c r="H8" s="17">
         <v>7</v>
       </c>
-      <c r="I8" s="21"/>
-      <c r="J8" s="22"/>
-      <c r="K8" s="23"/>
+      <c r="I8" s="20">
+        <f t="shared" si="3"/>
+        <v>1750000</v>
+      </c>
+      <c r="J8" s="21">
+        <f t="shared" si="4"/>
+        <v>262500</v>
+      </c>
+      <c r="K8" s="22">
+        <f t="shared" si="5"/>
+        <v>1487500</v>
+      </c>
       <c r="L8" s="5"/>
       <c r="M8" s="5"/>
       <c r="N8" s="5"/>
@@ -1190,15 +1276,33 @@
       <c r="D9" s="6" t="s">
         <v>14</v>
       </c>
-      <c r="E9" s="19"/>
-      <c r="F9" s="19"/>
-      <c r="G9" s="20"/>
+      <c r="E9" s="19" t="str">
+        <f t="shared" si="0"/>
+        <v>Ligna</v>
+      </c>
+      <c r="F9" s="19" t="str">
+        <f t="shared" si="1"/>
+        <v>MEJA BELAJAR</v>
+      </c>
+      <c r="G9" s="23">
+        <f t="shared" si="2"/>
+        <v>475000</v>
+      </c>
       <c r="H9" s="17">
         <v>9</v>
       </c>
-      <c r="I9" s="21"/>
-      <c r="J9" s="22"/>
-      <c r="K9" s="23"/>
+      <c r="I9" s="20">
+        <f t="shared" si="3"/>
+        <v>4275000</v>
+      </c>
+      <c r="J9" s="21">
+        <f t="shared" si="4"/>
+        <v>427500</v>
+      </c>
+      <c r="K9" s="22">
+        <f t="shared" si="5"/>
+        <v>3847500</v>
+      </c>
       <c r="L9" s="5"/>
       <c r="M9" s="5"/>
       <c r="N9" s="5"/>
@@ -1217,15 +1321,33 @@
       <c r="D10" s="6" t="s">
         <v>15</v>
       </c>
-      <c r="E10" s="19"/>
-      <c r="F10" s="19"/>
-      <c r="G10" s="20"/>
+      <c r="E10" s="19" t="str">
+        <f t="shared" si="0"/>
+        <v>Ligna</v>
+      </c>
+      <c r="F10" s="19" t="str">
+        <f t="shared" si="1"/>
+        <v>MEJA BELAJAR</v>
+      </c>
+      <c r="G10" s="23">
+        <f t="shared" si="2"/>
+        <v>475000</v>
+      </c>
       <c r="H10" s="17">
         <v>6</v>
       </c>
-      <c r="I10" s="21"/>
-      <c r="J10" s="22"/>
-      <c r="K10" s="23"/>
+      <c r="I10" s="20">
+        <f t="shared" si="3"/>
+        <v>2850000</v>
+      </c>
+      <c r="J10" s="21">
+        <f t="shared" si="4"/>
+        <v>570000</v>
+      </c>
+      <c r="K10" s="22">
+        <f t="shared" si="5"/>
+        <v>2280000</v>
+      </c>
       <c r="L10" s="5"/>
       <c r="M10" s="5"/>
       <c r="N10" s="5"/>
@@ -1244,15 +1366,33 @@
       <c r="D11" s="6" t="s">
         <v>16</v>
       </c>
-      <c r="E11" s="19"/>
-      <c r="F11" s="19"/>
-      <c r="G11" s="20"/>
+      <c r="E11" s="19" t="str">
+        <f t="shared" si="0"/>
+        <v>Olympic</v>
+      </c>
+      <c r="F11" s="19" t="str">
+        <f t="shared" si="1"/>
+        <v>MEJA KERJA</v>
+      </c>
+      <c r="G11" s="23">
+        <f t="shared" si="2"/>
+        <v>760000</v>
+      </c>
       <c r="H11" s="17">
         <v>7</v>
       </c>
-      <c r="I11" s="21"/>
-      <c r="J11" s="22"/>
-      <c r="K11" s="23"/>
+      <c r="I11" s="20">
+        <f t="shared" si="3"/>
+        <v>5320000</v>
+      </c>
+      <c r="J11" s="21">
+        <f t="shared" si="4"/>
+        <v>399000</v>
+      </c>
+      <c r="K11" s="22">
+        <f t="shared" si="5"/>
+        <v>4921000</v>
+      </c>
       <c r="L11" s="5"/>
       <c r="M11" s="5"/>
       <c r="N11" s="5"/>
@@ -1271,15 +1411,33 @@
       <c r="D12" s="6" t="s">
         <v>17</v>
       </c>
-      <c r="E12" s="19"/>
-      <c r="F12" s="19"/>
-      <c r="G12" s="20"/>
+      <c r="E12" s="19" t="str">
+        <f t="shared" si="0"/>
+        <v>Ligna</v>
+      </c>
+      <c r="F12" s="19" t="str">
+        <f t="shared" si="1"/>
+        <v>RAK BUKU</v>
+      </c>
+      <c r="G12" s="23">
+        <f t="shared" si="2"/>
+        <v>250000</v>
+      </c>
       <c r="H12" s="17">
         <v>11</v>
       </c>
-      <c r="I12" s="21"/>
-      <c r="J12" s="22"/>
-      <c r="K12" s="23"/>
+      <c r="I12" s="20">
+        <f t="shared" si="3"/>
+        <v>2750000</v>
+      </c>
+      <c r="J12" s="21">
+        <f t="shared" si="4"/>
+        <v>412500</v>
+      </c>
+      <c r="K12" s="22">
+        <f t="shared" si="5"/>
+        <v>2337500</v>
+      </c>
       <c r="L12" s="5"/>
       <c r="M12" s="5"/>
       <c r="N12" s="5"/>
@@ -1298,15 +1456,33 @@
       <c r="D13" s="6" t="s">
         <v>18</v>
       </c>
-      <c r="E13" s="19"/>
-      <c r="F13" s="19"/>
-      <c r="G13" s="20"/>
+      <c r="E13" s="19" t="str">
+        <f t="shared" si="0"/>
+        <v>Olympic</v>
+      </c>
+      <c r="F13" s="19" t="str">
+        <f t="shared" si="1"/>
+        <v>RAK BUKU</v>
+      </c>
+      <c r="G13" s="23">
+        <f t="shared" si="2"/>
+        <v>250000</v>
+      </c>
       <c r="H13" s="17">
         <v>11</v>
       </c>
-      <c r="I13" s="21"/>
-      <c r="J13" s="22"/>
-      <c r="K13" s="23"/>
+      <c r="I13" s="20">
+        <f t="shared" si="3"/>
+        <v>2750000</v>
+      </c>
+      <c r="J13" s="21">
+        <f t="shared" si="4"/>
+        <v>412500</v>
+      </c>
+      <c r="K13" s="22">
+        <f t="shared" si="5"/>
+        <v>2337500</v>
+      </c>
       <c r="L13" s="5"/>
       <c r="M13" s="5"/>
       <c r="N13" s="5"/>
@@ -1325,15 +1501,33 @@
       <c r="D14" s="6" t="s">
         <v>14</v>
       </c>
-      <c r="E14" s="19"/>
-      <c r="F14" s="19"/>
-      <c r="G14" s="20"/>
+      <c r="E14" s="19" t="str">
+        <f t="shared" si="0"/>
+        <v>Ligna</v>
+      </c>
+      <c r="F14" s="19" t="str">
+        <f t="shared" si="1"/>
+        <v>MEJA BELAJAR</v>
+      </c>
+      <c r="G14" s="23">
+        <f t="shared" si="2"/>
+        <v>475000</v>
+      </c>
       <c r="H14" s="17">
         <v>5</v>
       </c>
-      <c r="I14" s="21"/>
-      <c r="J14" s="22"/>
-      <c r="K14" s="23"/>
+      <c r="I14" s="20">
+        <f t="shared" si="3"/>
+        <v>2375000</v>
+      </c>
+      <c r="J14" s="21">
+        <f t="shared" si="4"/>
+        <v>237500</v>
+      </c>
+      <c r="K14" s="22">
+        <f t="shared" si="5"/>
+        <v>2137500</v>
+      </c>
       <c r="L14" s="5"/>
       <c r="M14" s="5"/>
       <c r="N14" s="5"/>
@@ -1352,15 +1546,33 @@
       <c r="D15" s="6" t="s">
         <v>19</v>
       </c>
-      <c r="E15" s="19"/>
-      <c r="F15" s="19"/>
-      <c r="G15" s="20"/>
+      <c r="E15" s="19" t="str">
+        <f t="shared" si="0"/>
+        <v>Garuda</v>
+      </c>
+      <c r="F15" s="19" t="str">
+        <f t="shared" si="1"/>
+        <v>MEJA BELAJAR</v>
+      </c>
+      <c r="G15" s="23">
+        <f t="shared" si="2"/>
+        <v>475000</v>
+      </c>
       <c r="H15" s="17">
         <v>10</v>
       </c>
-      <c r="I15" s="21"/>
-      <c r="J15" s="22"/>
-      <c r="K15" s="23"/>
+      <c r="I15" s="20">
+        <f t="shared" si="3"/>
+        <v>4750000</v>
+      </c>
+      <c r="J15" s="21">
+        <f t="shared" si="4"/>
+        <v>950000</v>
+      </c>
+      <c r="K15" s="22">
+        <f t="shared" si="5"/>
+        <v>3800000</v>
+      </c>
       <c r="L15" s="5"/>
       <c r="M15" s="5"/>
       <c r="N15" s="5"/>
@@ -1429,15 +1641,15 @@
       <c r="F18" s="2">
         <v>1</v>
       </c>
-      <c r="G18" s="29" t="s">
+      <c r="G18" s="24" t="s">
         <v>27</v>
       </c>
-      <c r="H18" s="29"/>
-      <c r="I18" s="29"/>
-      <c r="J18" s="29"/>
-      <c r="K18" s="29"/>
-      <c r="L18" s="29"/>
-      <c r="M18" s="29"/>
+      <c r="H18" s="24"/>
+      <c r="I18" s="24"/>
+      <c r="J18" s="24"/>
+      <c r="K18" s="24"/>
+      <c r="L18" s="24"/>
+      <c r="M18" s="24"/>
       <c r="N18" s="1"/>
       <c r="O18" s="1"/>
       <c r="P18" s="1"/>
@@ -1456,15 +1668,15 @@
       <c r="F19" s="2">
         <v>2</v>
       </c>
-      <c r="G19" s="29" t="s">
+      <c r="G19" s="24" t="s">
         <v>30</v>
       </c>
-      <c r="H19" s="29"/>
-      <c r="I19" s="29"/>
-      <c r="J19" s="29"/>
-      <c r="K19" s="29"/>
-      <c r="L19" s="29"/>
-      <c r="M19" s="29"/>
+      <c r="H19" s="24"/>
+      <c r="I19" s="24"/>
+      <c r="J19" s="24"/>
+      <c r="K19" s="24"/>
+      <c r="L19" s="24"/>
+      <c r="M19" s="24"/>
       <c r="N19" s="1"/>
       <c r="O19" s="1"/>
       <c r="P19" s="1"/>
@@ -1483,15 +1695,15 @@
       <c r="F20" s="2">
         <v>3</v>
       </c>
-      <c r="G20" s="29" t="s">
+      <c r="G20" s="24" t="s">
         <v>33</v>
       </c>
-      <c r="H20" s="29"/>
-      <c r="I20" s="29"/>
-      <c r="J20" s="29"/>
-      <c r="K20" s="29"/>
-      <c r="L20" s="29"/>
-      <c r="M20" s="29"/>
+      <c r="H20" s="24"/>
+      <c r="I20" s="24"/>
+      <c r="J20" s="24"/>
+      <c r="K20" s="24"/>
+      <c r="L20" s="24"/>
+      <c r="M20" s="24"/>
       <c r="N20" s="1"/>
       <c r="O20" s="1"/>
       <c r="P20" s="1"/>
@@ -1510,15 +1722,15 @@
       <c r="F21" s="2">
         <v>4</v>
       </c>
-      <c r="G21" s="29" t="s">
+      <c r="G21" s="24" t="s">
         <v>36</v>
       </c>
-      <c r="H21" s="29"/>
-      <c r="I21" s="29"/>
-      <c r="J21" s="29"/>
-      <c r="K21" s="29"/>
-      <c r="L21" s="29"/>
-      <c r="M21" s="29"/>
+      <c r="H21" s="24"/>
+      <c r="I21" s="24"/>
+      <c r="J21" s="24"/>
+      <c r="K21" s="24"/>
+      <c r="L21" s="24"/>
+      <c r="M21" s="24"/>
       <c r="N21" s="1"/>
       <c r="O21" s="1"/>
       <c r="P21" s="1"/>
@@ -1533,15 +1745,15 @@
       <c r="F22" s="2">
         <v>5</v>
       </c>
-      <c r="G22" s="29" t="s">
+      <c r="G22" s="24" t="s">
         <v>51</v>
       </c>
-      <c r="H22" s="29"/>
-      <c r="I22" s="29"/>
-      <c r="J22" s="29"/>
-      <c r="K22" s="29"/>
-      <c r="L22" s="29"/>
-      <c r="M22" s="29"/>
+      <c r="H22" s="24"/>
+      <c r="I22" s="24"/>
+      <c r="J22" s="24"/>
+      <c r="K22" s="24"/>
+      <c r="L22" s="24"/>
+      <c r="M22" s="24"/>
       <c r="N22" s="1"/>
       <c r="O22" s="1"/>
       <c r="P22" s="1"/>
@@ -1562,15 +1774,15 @@
       <c r="F23" s="2">
         <v>6</v>
       </c>
-      <c r="G23" s="29" t="s">
+      <c r="G23" s="24" t="s">
         <v>38</v>
       </c>
-      <c r="H23" s="29"/>
-      <c r="I23" s="29"/>
-      <c r="J23" s="29"/>
-      <c r="K23" s="29"/>
-      <c r="L23" s="29"/>
-      <c r="M23" s="29"/>
+      <c r="H23" s="24"/>
+      <c r="I23" s="24"/>
+      <c r="J23" s="24"/>
+      <c r="K23" s="24"/>
+      <c r="L23" s="24"/>
+      <c r="M23" s="24"/>
       <c r="N23" s="3"/>
       <c r="O23" s="3"/>
       <c r="P23" s="3"/>
@@ -1589,13 +1801,13 @@
       </c>
       <c r="E24" s="1"/>
       <c r="F24" s="2"/>
-      <c r="G24" s="29"/>
-      <c r="H24" s="29"/>
-      <c r="I24" s="29"/>
-      <c r="J24" s="29"/>
-      <c r="K24" s="29"/>
-      <c r="L24" s="29"/>
-      <c r="M24" s="29"/>
+      <c r="G24" s="24"/>
+      <c r="H24" s="24"/>
+      <c r="I24" s="24"/>
+      <c r="J24" s="24"/>
+      <c r="K24" s="24"/>
+      <c r="L24" s="24"/>
+      <c r="M24" s="24"/>
       <c r="N24" s="1"/>
       <c r="O24" s="1"/>
       <c r="P24" s="1"/>
@@ -1672,6 +1884,17 @@
     </row>
   </sheetData>
   <mergeCells count="18">
+    <mergeCell ref="E1:F1"/>
+    <mergeCell ref="H2:H3"/>
+    <mergeCell ref="I2:I3"/>
+    <mergeCell ref="J2:J3"/>
+    <mergeCell ref="K2:K3"/>
+    <mergeCell ref="G2:G3"/>
+    <mergeCell ref="B2:B3"/>
+    <mergeCell ref="C2:C3"/>
+    <mergeCell ref="D2:D3"/>
+    <mergeCell ref="E2:E3"/>
+    <mergeCell ref="F2:F3"/>
     <mergeCell ref="G23:M23"/>
     <mergeCell ref="G24:M24"/>
     <mergeCell ref="G18:M18"/>
@@ -1679,20 +1902,9 @@
     <mergeCell ref="G20:M20"/>
     <mergeCell ref="G21:M21"/>
     <mergeCell ref="G22:M22"/>
-    <mergeCell ref="B2:B3"/>
-    <mergeCell ref="C2:C3"/>
-    <mergeCell ref="D2:D3"/>
-    <mergeCell ref="E2:E3"/>
-    <mergeCell ref="F2:F3"/>
-    <mergeCell ref="E1:F1"/>
-    <mergeCell ref="H2:H3"/>
-    <mergeCell ref="I2:I3"/>
-    <mergeCell ref="J2:J3"/>
-    <mergeCell ref="K2:K3"/>
-    <mergeCell ref="G2:G3"/>
   </mergeCells>
   <hyperlinks>
-    <hyperlink ref="E1" r:id="rId1" xr:uid="{610E29A4-4243-4C8A-893D-287A8C59A938}"/>
+    <hyperlink ref="E1" r:id="rId1"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="0" verticalDpi="0" r:id="rId2"/>

--- a/exercise/Admin/Admin Penjualan/Tes Excel Admin Penjualan 8.xlsx
+++ b/exercise/Admin/Admin Penjualan/Tes Excel Admin Penjualan 8.xlsx
@@ -1,20 +1,21 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
-  <fileVersion appName="xl" lastEdited="6" lowestEdited="6" rupBuild="14420"/>
-  <workbookPr codeName="ThisWorkbook"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="26731"/>
+  <workbookPr codeName="ThisWorkbook" defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Pemrograman\Excel\excel\exercise\Admin\Admin Penjualan\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\admin\Downloads\Tes Excel Admin Penjualan 8\"/>
     </mc:Choice>
   </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0FAE3F38-675E-4B11-8E44-88BF1B96B38D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Soal" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="152511"/>
+  <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -376,7 +377,7 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="3">
     <numFmt numFmtId="41" formatCode="_-* #,##0_-;\-* #,##0_-;_-* &quot;-&quot;_-;_-@_-"/>
     <numFmt numFmtId="164" formatCode="_(* #,##0.00_);_(* \(#,##0.00\);_(* &quot;-&quot;??_);_(@_)"/>
@@ -547,7 +548,7 @@
     <xf numFmtId="41" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="30">
+  <cellXfs count="31">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
@@ -596,6 +597,9 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" indent="1"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="1" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
@@ -608,23 +612,23 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="5" xfId="4" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="5">
@@ -632,7 +636,7 @@
     <cellStyle name="Comma [0]" xfId="3" builtinId="6"/>
     <cellStyle name="Hyperlink" xfId="4" builtinId="8"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
-    <cellStyle name="Normal 2 2" xfId="2"/>
+    <cellStyle name="Normal 2 2" xfId="2" xr:uid="{00000000-0005-0000-0000-000002000000}"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -943,7 +947,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <sheetPr codeName="Sheet1">
     <tabColor theme="0"/>
   </sheetPr>
@@ -966,10 +970,10 @@
       <c r="D1" s="10" t="s">
         <v>56</v>
       </c>
-      <c r="E1" s="26" t="s">
+      <c r="E1" s="30" t="s">
         <v>57</v>
       </c>
-      <c r="F1" s="27"/>
+      <c r="F1" s="25"/>
       <c r="G1" s="2"/>
       <c r="H1" s="2"/>
       <c r="I1" s="2"/>
@@ -984,34 +988,34 @@
     </row>
     <row r="2" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A2" s="3"/>
-      <c r="B2" s="25" t="s">
+      <c r="B2" s="26" t="s">
         <v>0</v>
       </c>
-      <c r="C2" s="25" t="s">
+      <c r="C2" s="26" t="s">
         <v>1</v>
       </c>
-      <c r="D2" s="25" t="s">
+      <c r="D2" s="26" t="s">
         <v>2</v>
       </c>
-      <c r="E2" s="25" t="s">
+      <c r="E2" s="26" t="s">
         <v>3</v>
       </c>
-      <c r="F2" s="25" t="s">
+      <c r="F2" s="26" t="s">
         <v>4</v>
       </c>
-      <c r="G2" s="28" t="s">
+      <c r="G2" s="27" t="s">
         <v>5</v>
       </c>
-      <c r="H2" s="25" t="s">
+      <c r="H2" s="26" t="s">
         <v>6</v>
       </c>
-      <c r="I2" s="25" t="s">
+      <c r="I2" s="26" t="s">
         <v>7</v>
       </c>
-      <c r="J2" s="25" t="s">
+      <c r="J2" s="26" t="s">
         <v>8</v>
       </c>
-      <c r="K2" s="25" t="s">
+      <c r="K2" s="26" t="s">
         <v>9</v>
       </c>
       <c r="L2" s="3"/>
@@ -1023,16 +1027,16 @@
     </row>
     <row r="3" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A3" s="4"/>
-      <c r="B3" s="25"/>
-      <c r="C3" s="25"/>
-      <c r="D3" s="25"/>
-      <c r="E3" s="25"/>
-      <c r="F3" s="25"/>
-      <c r="G3" s="29"/>
-      <c r="H3" s="25"/>
-      <c r="I3" s="25"/>
-      <c r="J3" s="25"/>
-      <c r="K3" s="25"/>
+      <c r="B3" s="26"/>
+      <c r="C3" s="26"/>
+      <c r="D3" s="26"/>
+      <c r="E3" s="26"/>
+      <c r="F3" s="26"/>
+      <c r="G3" s="28"/>
+      <c r="H3" s="26"/>
+      <c r="I3" s="26"/>
+      <c r="J3" s="26"/>
+      <c r="K3" s="26"/>
       <c r="L3" s="4"/>
       <c r="M3" s="4"/>
       <c r="N3" s="4"/>
@@ -1051,33 +1055,15 @@
       <c r="D4" s="6" t="s">
         <v>10</v>
       </c>
-      <c r="E4" s="19" t="str">
-        <f>IF(LEFT(D4,1)="L","Ligna",IF(LEFT(D4,1)="O","Olympic",IF(LEFT(D4,1)="G","Garuda")))</f>
-        <v>Ligna</v>
-      </c>
-      <c r="F4" s="19" t="str">
-        <f>VLOOKUP(MID(D4,2,2),$C$17:$D$21,2,FALSE)</f>
-        <v>ALMARI</v>
-      </c>
-      <c r="G4" s="23">
-        <f>MID(D4,4,3)*1000</f>
-        <v>350000</v>
-      </c>
+      <c r="E4" s="19"/>
+      <c r="F4" s="19"/>
+      <c r="G4" s="24"/>
       <c r="H4" s="17">
         <v>6</v>
       </c>
-      <c r="I4" s="20">
-        <f>G4*H4</f>
-        <v>2100000</v>
-      </c>
-      <c r="J4" s="21">
-        <f>I4*(VLOOKUP(MID(D4,9,1),$C$23:$D$27,2,FALSE))</f>
-        <v>420000</v>
-      </c>
-      <c r="K4" s="22">
-        <f>I4-J4</f>
-        <v>1680000</v>
-      </c>
+      <c r="I4" s="21"/>
+      <c r="J4" s="22"/>
+      <c r="K4" s="23"/>
       <c r="L4" s="5"/>
       <c r="M4" s="5"/>
       <c r="N4" s="14"/>
@@ -1096,33 +1082,15 @@
       <c r="D5" s="6" t="s">
         <v>11</v>
       </c>
-      <c r="E5" s="19" t="str">
-        <f t="shared" ref="E5:E15" si="0">IF(LEFT(D5,1)="L","Ligna",IF(LEFT(D5,1)="O","Olympic",IF(LEFT(D5,1)="G","Garuda")))</f>
-        <v>Garuda</v>
-      </c>
-      <c r="F5" s="19" t="str">
-        <f t="shared" ref="F5:F15" si="1">VLOOKUP(MID(D5,2,2),$C$17:$D$21,2,FALSE)</f>
-        <v>RAK BUKU</v>
-      </c>
-      <c r="G5" s="23">
-        <f t="shared" ref="G5:G15" si="2">MID(D5,4,3)*1000</f>
-        <v>250000</v>
-      </c>
+      <c r="E5" s="19"/>
+      <c r="F5" s="19"/>
+      <c r="G5" s="20"/>
       <c r="H5" s="17">
         <v>7</v>
       </c>
-      <c r="I5" s="20">
-        <f t="shared" ref="I5:I15" si="3">G5*H5</f>
-        <v>1750000</v>
-      </c>
-      <c r="J5" s="21">
-        <f t="shared" ref="J5:J15" si="4">I5*(VLOOKUP(MID(D5,9,1),$C$23:$D$27,2,FALSE))</f>
-        <v>262500</v>
-      </c>
-      <c r="K5" s="22">
-        <f t="shared" ref="K5:K15" si="5">I5-J5</f>
-        <v>1487500</v>
-      </c>
+      <c r="I5" s="21"/>
+      <c r="J5" s="22"/>
+      <c r="K5" s="23"/>
       <c r="L5" s="5"/>
       <c r="M5" s="5"/>
       <c r="N5" s="5"/>
@@ -1141,33 +1109,15 @@
       <c r="D6" s="6" t="s">
         <v>12</v>
       </c>
-      <c r="E6" s="19" t="str">
-        <f t="shared" si="0"/>
-        <v>Olympic</v>
-      </c>
-      <c r="F6" s="19" t="str">
-        <f t="shared" si="1"/>
-        <v>MEJA BELAJAR</v>
-      </c>
-      <c r="G6" s="23">
-        <f t="shared" si="2"/>
-        <v>475000</v>
-      </c>
+      <c r="E6" s="19"/>
+      <c r="F6" s="19"/>
+      <c r="G6" s="20"/>
       <c r="H6" s="17">
         <v>10</v>
       </c>
-      <c r="I6" s="20">
-        <f t="shared" si="3"/>
-        <v>4750000</v>
-      </c>
-      <c r="J6" s="21">
-        <f t="shared" si="4"/>
-        <v>950000</v>
-      </c>
-      <c r="K6" s="22">
-        <f t="shared" si="5"/>
-        <v>3800000</v>
-      </c>
+      <c r="I6" s="21"/>
+      <c r="J6" s="22"/>
+      <c r="K6" s="23"/>
       <c r="L6" s="5"/>
       <c r="M6" s="5"/>
       <c r="N6" s="5"/>
@@ -1186,33 +1136,15 @@
       <c r="D7" s="6" t="s">
         <v>13</v>
       </c>
-      <c r="E7" s="19" t="str">
-        <f t="shared" si="0"/>
-        <v>Ligna</v>
-      </c>
-      <c r="F7" s="19" t="str">
-        <f t="shared" si="1"/>
-        <v>MEJA KERJA</v>
-      </c>
-      <c r="G7" s="23">
-        <f t="shared" si="2"/>
-        <v>760000</v>
-      </c>
+      <c r="E7" s="19"/>
+      <c r="F7" s="19"/>
+      <c r="G7" s="20"/>
       <c r="H7" s="17">
         <v>7</v>
       </c>
-      <c r="I7" s="20">
-        <f t="shared" si="3"/>
-        <v>5320000</v>
-      </c>
-      <c r="J7" s="21">
-        <f t="shared" si="4"/>
-        <v>532000</v>
-      </c>
-      <c r="K7" s="22">
-        <f t="shared" si="5"/>
-        <v>4788000</v>
-      </c>
+      <c r="I7" s="21"/>
+      <c r="J7" s="22"/>
+      <c r="K7" s="23"/>
       <c r="L7" s="5"/>
       <c r="M7" s="5"/>
       <c r="N7" s="5"/>
@@ -1231,33 +1163,15 @@
       <c r="D8" s="6" t="s">
         <v>11</v>
       </c>
-      <c r="E8" s="19" t="str">
-        <f t="shared" si="0"/>
-        <v>Garuda</v>
-      </c>
-      <c r="F8" s="19" t="str">
-        <f t="shared" si="1"/>
-        <v>RAK BUKU</v>
-      </c>
-      <c r="G8" s="23">
-        <f t="shared" si="2"/>
-        <v>250000</v>
-      </c>
+      <c r="E8" s="19"/>
+      <c r="F8" s="19"/>
+      <c r="G8" s="20"/>
       <c r="H8" s="17">
         <v>7</v>
       </c>
-      <c r="I8" s="20">
-        <f t="shared" si="3"/>
-        <v>1750000</v>
-      </c>
-      <c r="J8" s="21">
-        <f t="shared" si="4"/>
-        <v>262500</v>
-      </c>
-      <c r="K8" s="22">
-        <f t="shared" si="5"/>
-        <v>1487500</v>
-      </c>
+      <c r="I8" s="21"/>
+      <c r="J8" s="22"/>
+      <c r="K8" s="23"/>
       <c r="L8" s="5"/>
       <c r="M8" s="5"/>
       <c r="N8" s="5"/>
@@ -1276,33 +1190,15 @@
       <c r="D9" s="6" t="s">
         <v>14</v>
       </c>
-      <c r="E9" s="19" t="str">
-        <f t="shared" si="0"/>
-        <v>Ligna</v>
-      </c>
-      <c r="F9" s="19" t="str">
-        <f t="shared" si="1"/>
-        <v>MEJA BELAJAR</v>
-      </c>
-      <c r="G9" s="23">
-        <f t="shared" si="2"/>
-        <v>475000</v>
-      </c>
+      <c r="E9" s="19"/>
+      <c r="F9" s="19"/>
+      <c r="G9" s="20"/>
       <c r="H9" s="17">
         <v>9</v>
       </c>
-      <c r="I9" s="20">
-        <f t="shared" si="3"/>
-        <v>4275000</v>
-      </c>
-      <c r="J9" s="21">
-        <f t="shared" si="4"/>
-        <v>427500</v>
-      </c>
-      <c r="K9" s="22">
-        <f t="shared" si="5"/>
-        <v>3847500</v>
-      </c>
+      <c r="I9" s="21"/>
+      <c r="J9" s="22"/>
+      <c r="K9" s="23"/>
       <c r="L9" s="5"/>
       <c r="M9" s="5"/>
       <c r="N9" s="5"/>
@@ -1321,33 +1217,15 @@
       <c r="D10" s="6" t="s">
         <v>15</v>
       </c>
-      <c r="E10" s="19" t="str">
-        <f t="shared" si="0"/>
-        <v>Ligna</v>
-      </c>
-      <c r="F10" s="19" t="str">
-        <f t="shared" si="1"/>
-        <v>MEJA BELAJAR</v>
-      </c>
-      <c r="G10" s="23">
-        <f t="shared" si="2"/>
-        <v>475000</v>
-      </c>
+      <c r="E10" s="19"/>
+      <c r="F10" s="19"/>
+      <c r="G10" s="20"/>
       <c r="H10" s="17">
         <v>6</v>
       </c>
-      <c r="I10" s="20">
-        <f t="shared" si="3"/>
-        <v>2850000</v>
-      </c>
-      <c r="J10" s="21">
-        <f t="shared" si="4"/>
-        <v>570000</v>
-      </c>
-      <c r="K10" s="22">
-        <f t="shared" si="5"/>
-        <v>2280000</v>
-      </c>
+      <c r="I10" s="21"/>
+      <c r="J10" s="22"/>
+      <c r="K10" s="23"/>
       <c r="L10" s="5"/>
       <c r="M10" s="5"/>
       <c r="N10" s="5"/>
@@ -1366,33 +1244,15 @@
       <c r="D11" s="6" t="s">
         <v>16</v>
       </c>
-      <c r="E11" s="19" t="str">
-        <f t="shared" si="0"/>
-        <v>Olympic</v>
-      </c>
-      <c r="F11" s="19" t="str">
-        <f t="shared" si="1"/>
-        <v>MEJA KERJA</v>
-      </c>
-      <c r="G11" s="23">
-        <f t="shared" si="2"/>
-        <v>760000</v>
-      </c>
+      <c r="E11" s="19"/>
+      <c r="F11" s="19"/>
+      <c r="G11" s="20"/>
       <c r="H11" s="17">
         <v>7</v>
       </c>
-      <c r="I11" s="20">
-        <f t="shared" si="3"/>
-        <v>5320000</v>
-      </c>
-      <c r="J11" s="21">
-        <f t="shared" si="4"/>
-        <v>399000</v>
-      </c>
-      <c r="K11" s="22">
-        <f t="shared" si="5"/>
-        <v>4921000</v>
-      </c>
+      <c r="I11" s="21"/>
+      <c r="J11" s="22"/>
+      <c r="K11" s="23"/>
       <c r="L11" s="5"/>
       <c r="M11" s="5"/>
       <c r="N11" s="5"/>
@@ -1411,33 +1271,15 @@
       <c r="D12" s="6" t="s">
         <v>17</v>
       </c>
-      <c r="E12" s="19" t="str">
-        <f t="shared" si="0"/>
-        <v>Ligna</v>
-      </c>
-      <c r="F12" s="19" t="str">
-        <f t="shared" si="1"/>
-        <v>RAK BUKU</v>
-      </c>
-      <c r="G12" s="23">
-        <f t="shared" si="2"/>
-        <v>250000</v>
-      </c>
+      <c r="E12" s="19"/>
+      <c r="F12" s="19"/>
+      <c r="G12" s="20"/>
       <c r="H12" s="17">
         <v>11</v>
       </c>
-      <c r="I12" s="20">
-        <f t="shared" si="3"/>
-        <v>2750000</v>
-      </c>
-      <c r="J12" s="21">
-        <f t="shared" si="4"/>
-        <v>412500</v>
-      </c>
-      <c r="K12" s="22">
-        <f t="shared" si="5"/>
-        <v>2337500</v>
-      </c>
+      <c r="I12" s="21"/>
+      <c r="J12" s="22"/>
+      <c r="K12" s="23"/>
       <c r="L12" s="5"/>
       <c r="M12" s="5"/>
       <c r="N12" s="5"/>
@@ -1456,33 +1298,15 @@
       <c r="D13" s="6" t="s">
         <v>18</v>
       </c>
-      <c r="E13" s="19" t="str">
-        <f t="shared" si="0"/>
-        <v>Olympic</v>
-      </c>
-      <c r="F13" s="19" t="str">
-        <f t="shared" si="1"/>
-        <v>RAK BUKU</v>
-      </c>
-      <c r="G13" s="23">
-        <f t="shared" si="2"/>
-        <v>250000</v>
-      </c>
+      <c r="E13" s="19"/>
+      <c r="F13" s="19"/>
+      <c r="G13" s="20"/>
       <c r="H13" s="17">
         <v>11</v>
       </c>
-      <c r="I13" s="20">
-        <f t="shared" si="3"/>
-        <v>2750000</v>
-      </c>
-      <c r="J13" s="21">
-        <f t="shared" si="4"/>
-        <v>412500</v>
-      </c>
-      <c r="K13" s="22">
-        <f t="shared" si="5"/>
-        <v>2337500</v>
-      </c>
+      <c r="I13" s="21"/>
+      <c r="J13" s="22"/>
+      <c r="K13" s="23"/>
       <c r="L13" s="5"/>
       <c r="M13" s="5"/>
       <c r="N13" s="5"/>
@@ -1501,33 +1325,15 @@
       <c r="D14" s="6" t="s">
         <v>14</v>
       </c>
-      <c r="E14" s="19" t="str">
-        <f t="shared" si="0"/>
-        <v>Ligna</v>
-      </c>
-      <c r="F14" s="19" t="str">
-        <f t="shared" si="1"/>
-        <v>MEJA BELAJAR</v>
-      </c>
-      <c r="G14" s="23">
-        <f t="shared" si="2"/>
-        <v>475000</v>
-      </c>
+      <c r="E14" s="19"/>
+      <c r="F14" s="19"/>
+      <c r="G14" s="20"/>
       <c r="H14" s="17">
         <v>5</v>
       </c>
-      <c r="I14" s="20">
-        <f t="shared" si="3"/>
-        <v>2375000</v>
-      </c>
-      <c r="J14" s="21">
-        <f t="shared" si="4"/>
-        <v>237500</v>
-      </c>
-      <c r="K14" s="22">
-        <f t="shared" si="5"/>
-        <v>2137500</v>
-      </c>
+      <c r="I14" s="21"/>
+      <c r="J14" s="22"/>
+      <c r="K14" s="23"/>
       <c r="L14" s="5"/>
       <c r="M14" s="5"/>
       <c r="N14" s="5"/>
@@ -1546,33 +1352,15 @@
       <c r="D15" s="6" t="s">
         <v>19</v>
       </c>
-      <c r="E15" s="19" t="str">
-        <f t="shared" si="0"/>
-        <v>Garuda</v>
-      </c>
-      <c r="F15" s="19" t="str">
-        <f t="shared" si="1"/>
-        <v>MEJA BELAJAR</v>
-      </c>
-      <c r="G15" s="23">
-        <f t="shared" si="2"/>
-        <v>475000</v>
-      </c>
+      <c r="E15" s="19"/>
+      <c r="F15" s="19"/>
+      <c r="G15" s="20"/>
       <c r="H15" s="17">
         <v>10</v>
       </c>
-      <c r="I15" s="20">
-        <f t="shared" si="3"/>
-        <v>4750000</v>
-      </c>
-      <c r="J15" s="21">
-        <f t="shared" si="4"/>
-        <v>950000</v>
-      </c>
-      <c r="K15" s="22">
-        <f t="shared" si="5"/>
-        <v>3800000</v>
-      </c>
+      <c r="I15" s="21"/>
+      <c r="J15" s="22"/>
+      <c r="K15" s="23"/>
       <c r="L15" s="5"/>
       <c r="M15" s="5"/>
       <c r="N15" s="5"/>
@@ -1641,15 +1429,15 @@
       <c r="F18" s="2">
         <v>1</v>
       </c>
-      <c r="G18" s="24" t="s">
+      <c r="G18" s="29" t="s">
         <v>27</v>
       </c>
-      <c r="H18" s="24"/>
-      <c r="I18" s="24"/>
-      <c r="J18" s="24"/>
-      <c r="K18" s="24"/>
-      <c r="L18" s="24"/>
-      <c r="M18" s="24"/>
+      <c r="H18" s="29"/>
+      <c r="I18" s="29"/>
+      <c r="J18" s="29"/>
+      <c r="K18" s="29"/>
+      <c r="L18" s="29"/>
+      <c r="M18" s="29"/>
       <c r="N18" s="1"/>
       <c r="O18" s="1"/>
       <c r="P18" s="1"/>
@@ -1668,15 +1456,15 @@
       <c r="F19" s="2">
         <v>2</v>
       </c>
-      <c r="G19" s="24" t="s">
+      <c r="G19" s="29" t="s">
         <v>30</v>
       </c>
-      <c r="H19" s="24"/>
-      <c r="I19" s="24"/>
-      <c r="J19" s="24"/>
-      <c r="K19" s="24"/>
-      <c r="L19" s="24"/>
-      <c r="M19" s="24"/>
+      <c r="H19" s="29"/>
+      <c r="I19" s="29"/>
+      <c r="J19" s="29"/>
+      <c r="K19" s="29"/>
+      <c r="L19" s="29"/>
+      <c r="M19" s="29"/>
       <c r="N19" s="1"/>
       <c r="O19" s="1"/>
       <c r="P19" s="1"/>
@@ -1695,15 +1483,15 @@
       <c r="F20" s="2">
         <v>3</v>
       </c>
-      <c r="G20" s="24" t="s">
+      <c r="G20" s="29" t="s">
         <v>33</v>
       </c>
-      <c r="H20" s="24"/>
-      <c r="I20" s="24"/>
-      <c r="J20" s="24"/>
-      <c r="K20" s="24"/>
-      <c r="L20" s="24"/>
-      <c r="M20" s="24"/>
+      <c r="H20" s="29"/>
+      <c r="I20" s="29"/>
+      <c r="J20" s="29"/>
+      <c r="K20" s="29"/>
+      <c r="L20" s="29"/>
+      <c r="M20" s="29"/>
       <c r="N20" s="1"/>
       <c r="O20" s="1"/>
       <c r="P20" s="1"/>
@@ -1722,15 +1510,15 @@
       <c r="F21" s="2">
         <v>4</v>
       </c>
-      <c r="G21" s="24" t="s">
+      <c r="G21" s="29" t="s">
         <v>36</v>
       </c>
-      <c r="H21" s="24"/>
-      <c r="I21" s="24"/>
-      <c r="J21" s="24"/>
-      <c r="K21" s="24"/>
-      <c r="L21" s="24"/>
-      <c r="M21" s="24"/>
+      <c r="H21" s="29"/>
+      <c r="I21" s="29"/>
+      <c r="J21" s="29"/>
+      <c r="K21" s="29"/>
+      <c r="L21" s="29"/>
+      <c r="M21" s="29"/>
       <c r="N21" s="1"/>
       <c r="O21" s="1"/>
       <c r="P21" s="1"/>
@@ -1745,15 +1533,15 @@
       <c r="F22" s="2">
         <v>5</v>
       </c>
-      <c r="G22" s="24" t="s">
+      <c r="G22" s="29" t="s">
         <v>51</v>
       </c>
-      <c r="H22" s="24"/>
-      <c r="I22" s="24"/>
-      <c r="J22" s="24"/>
-      <c r="K22" s="24"/>
-      <c r="L22" s="24"/>
-      <c r="M22" s="24"/>
+      <c r="H22" s="29"/>
+      <c r="I22" s="29"/>
+      <c r="J22" s="29"/>
+      <c r="K22" s="29"/>
+      <c r="L22" s="29"/>
+      <c r="M22" s="29"/>
       <c r="N22" s="1"/>
       <c r="O22" s="1"/>
       <c r="P22" s="1"/>
@@ -1774,15 +1562,15 @@
       <c r="F23" s="2">
         <v>6</v>
       </c>
-      <c r="G23" s="24" t="s">
+      <c r="G23" s="29" t="s">
         <v>38</v>
       </c>
-      <c r="H23" s="24"/>
-      <c r="I23" s="24"/>
-      <c r="J23" s="24"/>
-      <c r="K23" s="24"/>
-      <c r="L23" s="24"/>
-      <c r="M23" s="24"/>
+      <c r="H23" s="29"/>
+      <c r="I23" s="29"/>
+      <c r="J23" s="29"/>
+      <c r="K23" s="29"/>
+      <c r="L23" s="29"/>
+      <c r="M23" s="29"/>
       <c r="N23" s="3"/>
       <c r="O23" s="3"/>
       <c r="P23" s="3"/>
@@ -1801,13 +1589,13 @@
       </c>
       <c r="E24" s="1"/>
       <c r="F24" s="2"/>
-      <c r="G24" s="24"/>
-      <c r="H24" s="24"/>
-      <c r="I24" s="24"/>
-      <c r="J24" s="24"/>
-      <c r="K24" s="24"/>
-      <c r="L24" s="24"/>
-      <c r="M24" s="24"/>
+      <c r="G24" s="29"/>
+      <c r="H24" s="29"/>
+      <c r="I24" s="29"/>
+      <c r="J24" s="29"/>
+      <c r="K24" s="29"/>
+      <c r="L24" s="29"/>
+      <c r="M24" s="29"/>
       <c r="N24" s="1"/>
       <c r="O24" s="1"/>
       <c r="P24" s="1"/>
@@ -1884,17 +1672,6 @@
     </row>
   </sheetData>
   <mergeCells count="18">
-    <mergeCell ref="E1:F1"/>
-    <mergeCell ref="H2:H3"/>
-    <mergeCell ref="I2:I3"/>
-    <mergeCell ref="J2:J3"/>
-    <mergeCell ref="K2:K3"/>
-    <mergeCell ref="G2:G3"/>
-    <mergeCell ref="B2:B3"/>
-    <mergeCell ref="C2:C3"/>
-    <mergeCell ref="D2:D3"/>
-    <mergeCell ref="E2:E3"/>
-    <mergeCell ref="F2:F3"/>
     <mergeCell ref="G23:M23"/>
     <mergeCell ref="G24:M24"/>
     <mergeCell ref="G18:M18"/>
@@ -1902,9 +1679,20 @@
     <mergeCell ref="G20:M20"/>
     <mergeCell ref="G21:M21"/>
     <mergeCell ref="G22:M22"/>
+    <mergeCell ref="B2:B3"/>
+    <mergeCell ref="C2:C3"/>
+    <mergeCell ref="D2:D3"/>
+    <mergeCell ref="E2:E3"/>
+    <mergeCell ref="F2:F3"/>
+    <mergeCell ref="E1:F1"/>
+    <mergeCell ref="H2:H3"/>
+    <mergeCell ref="I2:I3"/>
+    <mergeCell ref="J2:J3"/>
+    <mergeCell ref="K2:K3"/>
+    <mergeCell ref="G2:G3"/>
   </mergeCells>
   <hyperlinks>
-    <hyperlink ref="E1" r:id="rId1"/>
+    <hyperlink ref="E1" r:id="rId1" xr:uid="{610E29A4-4243-4C8A-893D-287A8C59A938}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="0" verticalDpi="0" r:id="rId2"/>
